--- a/data/trending_integrated_20261016_13.xlsx
+++ b/data/trending_integrated_20261016_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8700</v>
+        <v>8830</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.68%</t>
+          <t>'+23.50%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G2" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="H2" t="n">
         <v>0.72</v>
@@ -610,7 +610,7 @@
         <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>191776658350</v>
+        <v>200124961355</v>
       </c>
       <c r="P2" t="n">
         <v>8970</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>인수합병 가능성 및 뉴로메가 편입 사례를 통한 높은 상승 기대감 표출. 현재 주가 흐름에 대한 긍정적 언급 및 막판 거래량 증가 주목.</t>
+          <t>인수합병 시작 가능성 언급. 뉴로메가 편입 사례 비교하며 높은 기대감 표출. 거래량 증가.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['인수합병', '텐버거', '거래량']</t>
+          <t>['인수합병', '편입', '거래량']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7890</v>
+        <v>7840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.09%</t>
+          <t>'+19.33%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H3" t="n">
         <v>0.73</v>
@@ -702,7 +702,7 @@
         <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>71427509715</v>
+        <v>71776469745</v>
       </c>
       <c r="P3" t="n">
         <v>10300</v>
@@ -768,7 +768,7 @@
         <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>49992913995</v>
+        <v>50625253360</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9460</v>
+        <v>9480</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.01%</t>
+          <t>'+7.24%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>85215010985</v>
+        <v>86288210950</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66100</v>
+        <v>10360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.42%</t>
+          <t>'+4.33%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>429</v>
+        <v>144</v>
       </c>
       <c r="H6" t="n">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,91 +963,91 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>63300</v>
+        <v>9930</v>
       </c>
       <c r="K6" t="n">
-        <v>63900</v>
+        <v>10100</v>
       </c>
       <c r="L6" t="n">
-        <v>66200</v>
+        <v>11100</v>
       </c>
       <c r="M6" t="n">
-        <v>63500</v>
+        <v>9860</v>
       </c>
       <c r="N6" t="n">
-        <v>22.11</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>96926656450</v>
+        <v>31714621800</v>
       </c>
       <c r="P6" t="n">
-        <v>139200</v>
+        <v>19380</v>
       </c>
       <c r="Q6" t="n">
-        <v>57000</v>
+        <v>3200</v>
       </c>
       <c r="R6" t="n">
-        <v>50000</v>
+        <v>-140000</v>
       </c>
       <c r="S6" t="n">
-        <v>-24000</v>
+        <v>-3000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>뉴스케일파워 등 원전 관련 섹터 상승세 언급. 3분기 매출 하회 소식 및 주주 환원 정책 촉구.</t>
+          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', '매출', '주주환원']</t>
+          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10350</v>
+        <v>219000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.23%</t>
+          <t>'+4.29%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>495</v>
       </c>
       <c r="G7" t="n">
-        <v>142</v>
+        <v>1177</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>45.98</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9930</v>
+        <v>210000</v>
       </c>
       <c r="K7" t="n">
-        <v>10100</v>
+        <v>215000</v>
       </c>
       <c r="L7" t="n">
-        <v>11100</v>
+        <v>220500</v>
       </c>
       <c r="M7" t="n">
-        <v>9860</v>
+        <v>210500</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>46.16</v>
       </c>
       <c r="O7" t="n">
-        <v>31500069060</v>
+        <v>2434688477000</v>
       </c>
       <c r="P7" t="n">
-        <v>19380</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>3200</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>-140000</v>
+        <v>-684000</v>
       </c>
       <c r="S7" t="n">
-        <v>-3000</v>
+        <v>-108000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
+          <t>이재명 및 민주당 정책 관련 부정적 전망과 노조 성과급 지급 관련 불만 제기. 미국 CNBC 삼성전자 뉴스 언급 및 애플의 중국산 반도체 사용 검토 소식에 따른 향후 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
+          <t>['이평선', '매크로', '뉴스']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18930</v>
+        <v>65900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.18%</t>
+          <t>'+4.11%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="G8" t="n">
-        <v>168</v>
+        <v>443</v>
       </c>
       <c r="H8" t="n">
-        <v>27.77</v>
+        <v>22.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18170</v>
+        <v>63300</v>
       </c>
       <c r="K8" t="n">
-        <v>18340</v>
+        <v>63900</v>
       </c>
       <c r="L8" t="n">
-        <v>18990</v>
+        <v>66200</v>
       </c>
       <c r="M8" t="n">
-        <v>18110</v>
+        <v>63500</v>
       </c>
       <c r="N8" t="n">
-        <v>27.82</v>
+        <v>22.11</v>
       </c>
       <c r="O8" t="n">
-        <v>36635608940</v>
+        <v>98370742100</v>
       </c>
       <c r="P8" t="n">
-        <v>35350</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>17210</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>312000</v>
+        <v>50000</v>
       </c>
       <c r="S8" t="n">
-        <v>106000</v>
+        <v>-24000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
+          <t>뉴스케일파워 상승 마감 및 원전 관련 언급. 3분기 매출 하회 예상 및 신용 매도 지적.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
+          <t>['뉴스케일파워', '원전', '매출']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>218750</v>
+        <v>18860</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.17%</t>
+          <t>'+3.80%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.18</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>53</v>
       </c>
       <c r="F9" t="n">
-        <v>493</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>1168</v>
+        <v>170</v>
       </c>
       <c r="H9" t="n">
-        <v>45.98</v>
+        <v>27.77</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,143 +1239,143 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>210000</v>
+        <v>18170</v>
       </c>
       <c r="K9" t="n">
-        <v>215000</v>
+        <v>18340</v>
       </c>
       <c r="L9" t="n">
-        <v>219000</v>
+        <v>18990</v>
       </c>
       <c r="M9" t="n">
-        <v>210500</v>
+        <v>18110</v>
       </c>
       <c r="N9" t="n">
-        <v>46.16</v>
+        <v>27.82</v>
       </c>
       <c r="O9" t="n">
-        <v>2280919372750</v>
+        <v>38234528255</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>35350</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>17210</v>
       </c>
       <c r="R9" t="n">
-        <v>-684000</v>
+        <v>312000</v>
       </c>
       <c r="S9" t="n">
-        <v>-108000</v>
+        <v>106000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>이재명 및 민주당 정책 관련 부정적 전망과 노조 성과급 지급 관련 불만 제기. 미국 CNBC 삼성전자 뉴스 언급 및 애플의 중국산 반도체 사용 검토 소식에 따른 향후 주가 상승 기대.</t>
+          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['이평선', '매크로', '뉴스']</t>
+          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1309000</v>
+        <v>18100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.72%</t>
+          <t>'+3.61%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>168</v>
       </c>
       <c r="F10" t="n">
-        <v>513</v>
+        <v>97</v>
       </c>
       <c r="G10" t="n">
-        <v>1383</v>
+        <v>384</v>
       </c>
       <c r="H10" t="n">
-        <v>48.85</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1262000</v>
+        <v>17470</v>
       </c>
       <c r="K10" t="n">
-        <v>1290000</v>
+        <v>18710</v>
       </c>
       <c r="L10" t="n">
-        <v>1310000</v>
+        <v>20300</v>
       </c>
       <c r="M10" t="n">
-        <v>1247000</v>
+        <v>17630</v>
       </c>
       <c r="N10" t="n">
-        <v>49.02</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3560176356500</v>
+        <v>154986498130</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>28800</v>
       </c>
       <c r="Q10" t="n">
-        <v>420500</v>
+        <v>15780</v>
       </c>
       <c r="R10" t="n">
-        <v>-448000</v>
+        <v>3000</v>
       </c>
       <c r="S10" t="n">
-        <v>-27000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>최태원 회장 경영 비판 및 주가 관리 촉구. 외인 매도 지속 및 솔리다임 상장 이슈 언급.</t>
+          <t>반도체 공급망 확충 및 글로벌 파운드리 연내 착공 속 수혜주 언급. 2만원 돌파 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['경영', '외인', '이슈']</t>
+          <t>['반도체', '공급망', '파운드리']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42250</v>
+        <v>1305000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.68%</t>
+          <t>'+3.41%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.13</v>
+        <v>-0.17</v>
       </c>
       <c r="E11" t="n">
-        <v>240</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>129</v>
+        <v>514</v>
       </c>
       <c r="G11" t="n">
-        <v>974</v>
+        <v>1364</v>
       </c>
       <c r="H11" t="n">
-        <v>12.97</v>
+        <v>48.85</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>40750</v>
+        <v>1262000</v>
       </c>
       <c r="K11" t="n">
-        <v>40600</v>
+        <v>1290000</v>
       </c>
       <c r="L11" t="n">
-        <v>42300</v>
+        <v>1318000</v>
       </c>
       <c r="M11" t="n">
-        <v>40050</v>
+        <v>1247000</v>
       </c>
       <c r="N11" t="n">
-        <v>12.84</v>
+        <v>49.02</v>
       </c>
       <c r="O11" t="n">
-        <v>12775455325</v>
+        <v>3712819328500</v>
       </c>
       <c r="P11" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>24150</v>
+        <v>420500</v>
       </c>
       <c r="R11" t="n">
-        <v>15000</v>
+        <v>-448000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-27000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>CLASS1 발표에 대한 강한 기대감과 함께 FDA 승인 가능성 언급. 야간 선물 폭등 및 김태한 회장에 대한 신뢰를 바탕으로 한 주가 상승 전망.</t>
+          <t>최태원 회장에게 주가 관리 촉구. 연준 의장 연설 및 지정학적 이슈 언급. 외국인 매도 지속.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['CLASS1', 'FDA승인', 'IR']</t>
+          <t>['주가 관리', '외국인', '솔리다임']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13510</v>
+        <v>13430</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.45%</t>
+          <t>'+2.83%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="H12" t="n">
         <v>3.42</v>
@@ -1530,7 +1530,7 @@
         <v>3.21</v>
       </c>
       <c r="O12" t="n">
-        <v>39553834015</v>
+        <v>40542319235</v>
       </c>
       <c r="P12" t="n">
         <v>31500</v>
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15150</v>
+        <v>41900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.27%</t>
+          <t>'+2.82%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="E13" t="n">
-        <v>181</v>
+        <v>252</v>
       </c>
       <c r="F13" t="n">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="G13" t="n">
-        <v>399</v>
+        <v>989</v>
       </c>
       <c r="H13" t="n">
-        <v>9.779999999999999</v>
+        <v>12.97</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14670</v>
+        <v>40750</v>
       </c>
       <c r="K13" t="n">
-        <v>14800</v>
+        <v>40600</v>
       </c>
       <c r="L13" t="n">
-        <v>15270</v>
+        <v>42300</v>
       </c>
       <c r="M13" t="n">
-        <v>14800</v>
+        <v>40050</v>
       </c>
       <c r="N13" t="n">
-        <v>9.710000000000001</v>
+        <v>12.84</v>
       </c>
       <c r="O13" t="n">
-        <v>28850937010</v>
+        <v>13202584800</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>69200</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>24150</v>
       </c>
       <c r="R13" t="n">
-        <v>-92000</v>
+        <v>15000</v>
       </c>
       <c r="S13" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대우건설 단일판매 공시, 내년 건설주 상승 전망. 금감원 사모펀드 긴급 점검, 주가 조작 관련 언급. 주주 대차 해지 중요성 강조.</t>
+          <t>CLASS1 발표 임박 및 FDA 승인 기대감. 담관암 치료제 관련 긍정적 전망 제기. 미선물 동향 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공시', '건설주', '사모펀드']</t>
+          <t>['CLASS1', 'FDA 승인', '담관암']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,77 +1660,77 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17970</v>
+        <v>15040</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.86%</t>
+          <t>'+2.52%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="F14" t="n">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="G14" t="n">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>17470</v>
+        <v>14670</v>
       </c>
       <c r="K14" t="n">
-        <v>18710</v>
+        <v>14800</v>
       </c>
       <c r="L14" t="n">
-        <v>20300</v>
+        <v>15270</v>
       </c>
       <c r="M14" t="n">
-        <v>17630</v>
+        <v>14800</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>152931746605</v>
+        <v>29651311115</v>
       </c>
       <c r="P14" t="n">
-        <v>28800</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>15780</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>3000</v>
+        <v>-92000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반도체 테마 관련주로 일본/호남 반도체 공장 수혜 기대. 글로벌 파운드리 연내 착공 속보 언급.</t>
+          <t>단일판매·공급계약 체결 공시 확인. 주가 조작 및 금감원 사모펀드 점검 관련 언급. 외인 보유율 유지 관련 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체', '수혜', '파운드리']</t>
+          <t>['공시', '주가 조작', '외국인']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,86 +1752,86 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23700</v>
+        <v>15300</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.16%</t>
+          <t>'+2.41%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>64</v>
+        <v>172</v>
       </c>
       <c r="F15" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="G15" t="n">
-        <v>388</v>
+        <v>219</v>
       </c>
       <c r="H15" t="n">
-        <v>9.23</v>
+        <v>0.11</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>23200</v>
+        <v>14940</v>
       </c>
       <c r="K15" t="n">
-        <v>23250</v>
+        <v>14940</v>
       </c>
       <c r="L15" t="n">
-        <v>24250</v>
+        <v>16290</v>
       </c>
       <c r="M15" t="n">
-        <v>22900</v>
+        <v>14330</v>
       </c>
       <c r="N15" t="n">
-        <v>9.210000000000001</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>38283954750</v>
+        <v>45233812335</v>
       </c>
       <c r="P15" t="n">
-        <v>24950</v>
+        <v>30800</v>
       </c>
       <c r="Q15" t="n">
-        <v>17910</v>
+        <v>9810</v>
       </c>
       <c r="R15" t="n">
-        <v>435000</v>
+        <v>7000</v>
       </c>
       <c r="S15" t="n">
-        <v>-20000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
+          <t>상장 사기 및 높은 공모가 비판. 경영진 사퇴 요구 및 자진상폐 촉구.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['운항수익', '영업이익', 'SCFI']</t>
+          <t>['상장 사기', '공모가', '경영진']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,91 +1839,91 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14940</v>
+        <v>23650</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+1.94%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>170</v>
+        <v>66</v>
       </c>
       <c r="F16" t="n">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>215</v>
+        <v>395</v>
       </c>
       <c r="H16" t="n">
-        <v>0.11</v>
+        <v>9.23</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14940</v>
+        <v>23200</v>
       </c>
       <c r="K16" t="n">
-        <v>14940</v>
+        <v>23250</v>
       </c>
       <c r="L16" t="n">
-        <v>16290</v>
+        <v>24250</v>
       </c>
       <c r="M16" t="n">
-        <v>14330</v>
+        <v>22900</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>44578327215</v>
+        <v>39266909900</v>
       </c>
       <c r="P16" t="n">
-        <v>30800</v>
+        <v>24950</v>
       </c>
       <c r="Q16" t="n">
-        <v>9810</v>
+        <v>17910</v>
       </c>
       <c r="R16" t="n">
-        <v>7000</v>
+        <v>435000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-20000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>높은 공모가 및 상장 과정에 대한 비판과 함께 '상장사기', '초뻥튀기상장' 등의 표현 사용. 경영진 사퇴 촉구 및 자진 상폐 요구.</t>
+          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공모가', '상장사기', '자진상폐']</t>
+          <t>['운항수익', '영업이익', 'SCFI']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>011200</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20600</v>
+        <v>20700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.72%</t>
+          <t>'-0.24%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2.5</v>
       </c>
       <c r="E17" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F17" t="n">
         <v>70</v>
       </c>
       <c r="G17" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H17" t="n">
         <v>4.28</v>
@@ -1990,7 +1990,7 @@
         <v>1.78</v>
       </c>
       <c r="O17" t="n">
-        <v>65353410645</v>
+        <v>66960487370</v>
       </c>
       <c r="P17" t="n">
         <v>22450</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>농협, KDB 등 신규 납품 요청 및 보안 투자 확대 뉴스 기반 상승 기대. 양자보안 관련 내용 언급.</t>
+          <t>신규 납품 요청 및 보안 투자 확대 뉴스 기반. 양자보안 관련 기대감. 외인 및 연기금 매수세 확인.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['보안', '납품', '투자']</t>
+          <t>['양자보안', '납품', '보안 투자']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,27 +2039,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26850</v>
+        <v>26700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.83%</t>
+          <t>'-9.34%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F18" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G18" t="n">
-        <v>426</v>
+        <v>473</v>
       </c>
       <c r="H18" t="n">
-        <v>53.39</v>
+        <v>53.38</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2076,13 +2076,13 @@
         <v>29600</v>
       </c>
       <c r="M18" t="n">
-        <v>26750</v>
+        <v>26650</v>
       </c>
       <c r="N18" t="n">
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>132346389600</v>
+        <v>138657475475</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 발표 후 저점 매수 기회 언급과 함께 외인 매도 시작 및 프로그램 매도에 대한 우려 제기. 유튜버 및 특정 세력에 대한 불신 표현.</t>
+          <t>실적 발표 후 배당 기대감 속 저점 매수 기회 언급. 외국인 매도 및 주가 하락 전망 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적발표', '외인매도', '프로그램']</t>
+          <t>['배당', '실적', '외국인']</t>
         </is>
       </c>
       <c r="X18" t="n">

--- a/data/trending_integrated_20261016_13.xlsx
+++ b/data/trending_integrated_20261016_13.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8830</v>
+        <v>8040</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+23.50%</t>
+          <t>'+22.37%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.12</v>
+        <v>-0.26</v>
       </c>
       <c r="E2" t="n">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="F2" t="n">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>298</v>
+        <v>218</v>
       </c>
       <c r="H2" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,38 +595,38 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7150</v>
+        <v>6570</v>
       </c>
       <c r="K2" t="n">
-        <v>7430</v>
+        <v>6850</v>
       </c>
       <c r="L2" t="n">
-        <v>8970</v>
+        <v>8540</v>
       </c>
       <c r="M2" t="n">
-        <v>7300</v>
+        <v>6630</v>
       </c>
       <c r="N2" t="n">
-        <v>1.84</v>
+        <v>0.99</v>
       </c>
       <c r="O2" t="n">
-        <v>200124961355</v>
+        <v>73213665415</v>
       </c>
       <c r="P2" t="n">
-        <v>8970</v>
+        <v>10300</v>
       </c>
       <c r="Q2" t="n">
-        <v>2270</v>
+        <v>952</v>
       </c>
       <c r="R2" t="n">
-        <v>47000</v>
+        <v>-9000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>인수합병 시작 가능성 언급. 뉴로메가 편입 사례 비교하며 높은 기대감 표출. 거래량 증가.</t>
+          <t>군공항 이전 관련 언급 및 호남 반도체 관련주 상승 기대. 투경 및 급락 주의보, 외인 매수 전환 가능성 등 단기 변동성에 대한 다양한 의견.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,11 +635,11 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['인수합병', '편입', '거래량']</t>
+          <t>['군공항 이전', '호남 반도체', '투경']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7840</v>
+        <v>8740</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.33%</t>
+          <t>'+22.24%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.26</v>
+        <v>-1.12</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="G3" t="n">
-        <v>207</v>
+        <v>299</v>
       </c>
       <c r="H3" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6570</v>
+        <v>7150</v>
       </c>
       <c r="K3" t="n">
-        <v>6850</v>
+        <v>7430</v>
       </c>
       <c r="L3" t="n">
-        <v>8540</v>
+        <v>8970</v>
       </c>
       <c r="M3" t="n">
-        <v>6630</v>
+        <v>7300</v>
       </c>
       <c r="N3" t="n">
-        <v>0.99</v>
+        <v>1.84</v>
       </c>
       <c r="O3" t="n">
-        <v>71776469745</v>
+        <v>203400663915</v>
       </c>
       <c r="P3" t="n">
-        <v>10300</v>
+        <v>8970</v>
       </c>
       <c r="Q3" t="n">
-        <v>952</v>
+        <v>2270</v>
       </c>
       <c r="R3" t="n">
-        <v>-8000</v>
+        <v>36000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>군공항 이전 관련 이슈 언급 및 신고가 돌파 기대감 표출. 정치권 언급 및 외인 동향 주시.</t>
+          <t>인수합병 가능성 및 텐버거 기대감 있으나, 검은머리 외국인 향방, 매도 대응 언급 등 단기적 등락에 대한 혼재된 의견.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['군공항', '신고가', '외인']</t>
+          <t>['인수합병', '텐버거', '단타']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8190</v>
+        <v>8160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.55%</t>
+          <t>'+14.13%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
         <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>50625253360</v>
+        <v>50863624055</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -803,7 +803,7 @@
         <v>1206</v>
       </c>
       <c r="R4" t="n">
-        <v>-7000</v>
+        <v>231000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9480</v>
+        <v>9610</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.24%</t>
+          <t>'+8.71%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5" t="n">
         <v>148</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>86288210950</v>
+        <v>86799518455</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -895,7 +895,7 @@
         <v>465</v>
       </c>
       <c r="R5" t="n">
-        <v>-160000</v>
+        <v>-157000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10360</v>
+        <v>10410</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.33%</t>
+          <t>'+4.83%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>31714621800</v>
+        <v>31891008865</v>
       </c>
       <c r="P6" t="n">
         <v>19380</v>
@@ -987,10 +987,10 @@
         <v>3200</v>
       </c>
       <c r="R6" t="n">
-        <v>-140000</v>
+        <v>-121000</v>
       </c>
       <c r="S6" t="n">
-        <v>-3000</v>
+        <v>-8000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G7" t="n">
-        <v>1177</v>
+        <v>1236</v>
       </c>
       <c r="H7" t="n">
         <v>45.98</v>
@@ -1070,7 +1070,7 @@
         <v>46.16</v>
       </c>
       <c r="O7" t="n">
-        <v>2434688477000</v>
+        <v>2510362927750</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1079,23 +1079,23 @@
         <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>-684000</v>
+        <v>-231000</v>
       </c>
       <c r="S7" t="n">
-        <v>-108000</v>
+        <v>-192000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>이재명 및 민주당 정책 관련 부정적 전망과 노조 성과급 지급 관련 불만 제기. 미국 CNBC 삼성전자 뉴스 언급 및 애플의 중국산 반도체 사용 검토 소식에 따른 향후 주가 상승 기대.</t>
+          <t>금감원, 이재명 관련 논란 속 대책 논의. 미국 CNBC 보도 및 애플의 중국산 반도체 사용 검토 뉴스. 개인 투자자들의 부정적 전망과 기대 혼재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['이평선', '매크로', '뉴스']</t>
+          <t>['이재명', '금감원', 'CNBC']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,70 +1115,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>65900</v>
+        <v>18170</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.11%</t>
+          <t>'+4.01%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="F8" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G8" t="n">
-        <v>443</v>
+        <v>378</v>
       </c>
       <c r="H8" t="n">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>63300</v>
+        <v>17470</v>
       </c>
       <c r="K8" t="n">
-        <v>63900</v>
+        <v>18710</v>
       </c>
       <c r="L8" t="n">
-        <v>66200</v>
+        <v>20300</v>
       </c>
       <c r="M8" t="n">
-        <v>63500</v>
+        <v>17630</v>
       </c>
       <c r="N8" t="n">
-        <v>22.11</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>98370742100</v>
+        <v>155789369280</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>28800</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>15780</v>
       </c>
       <c r="R8" t="n">
-        <v>50000</v>
+        <v>4000</v>
       </c>
       <c r="S8" t="n">
-        <v>-24000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>뉴스케일파워 상승 마감 및 원전 관련 언급. 3분기 매출 하회 예상 및 신용 매도 지적.</t>
+          <t>반도체 테마 관련 언급 있으나, 장세 및 시가총액 고려 시 고평가 우려. 단일계좌 투주 이슈 및 단기 급락 가능성 경고.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['뉴스케일파워', '원전', '매출']</t>
+          <t>['반도체 테마', '단일계좌', '고평가']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,182 +1200,182 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18860</v>
+        <v>15530</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.80%</t>
+          <t>'+3.95%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>183</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="G9" t="n">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c r="H9" t="n">
-        <v>27.77</v>
+        <v>0.11</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18170</v>
+        <v>14940</v>
       </c>
       <c r="K9" t="n">
-        <v>18340</v>
+        <v>14940</v>
       </c>
       <c r="L9" t="n">
-        <v>18990</v>
+        <v>16290</v>
       </c>
       <c r="M9" t="n">
-        <v>18110</v>
+        <v>14330</v>
       </c>
       <c r="N9" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>38234528255</v>
+        <v>50437359945</v>
       </c>
       <c r="P9" t="n">
-        <v>35350</v>
+        <v>30800</v>
       </c>
       <c r="Q9" t="n">
-        <v>17210</v>
+        <v>9810</v>
       </c>
       <c r="R9" t="n">
-        <v>312000</v>
+        <v>6000</v>
       </c>
       <c r="S9" t="n">
-        <v>106000</v>
+        <v>2000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
+          <t>상장 사기 및 높은 공모가 비판. 경영진 사퇴 요구 및 자진상폐 촉구.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
+          <t>['상장 사기', '공모가', '경영진']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18100</v>
+        <v>65800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.61%</t>
+          <t>'+3.95%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="F10" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G10" t="n">
-        <v>384</v>
+        <v>443</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17470</v>
+        <v>63300</v>
       </c>
       <c r="K10" t="n">
-        <v>18710</v>
+        <v>63900</v>
       </c>
       <c r="L10" t="n">
-        <v>20300</v>
+        <v>66200</v>
       </c>
       <c r="M10" t="n">
-        <v>17630</v>
+        <v>63500</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>22.11</v>
       </c>
       <c r="O10" t="n">
-        <v>154986498130</v>
+        <v>100640667500</v>
       </c>
       <c r="P10" t="n">
-        <v>28800</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>15780</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>3000</v>
+        <v>78000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>반도체 공급망 확충 및 글로벌 파운드리 연내 착공 속 수혜주 언급. 2만원 돌파 기대감.</t>
+          <t>뉴스케일파워 상승 마감 및 원전 관련 언급. 3분기 매출 하회 예상 및 신용 매도 지적.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '공급망', '파운드리']</t>
+          <t>['뉴스케일파워', '원전', '매출']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1305000</v>
+        <v>18800</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.41%</t>
+          <t>'+3.47%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.17</v>
+        <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>54</v>
       </c>
       <c r="F11" t="n">
-        <v>514</v>
+        <v>34</v>
       </c>
       <c r="G11" t="n">
-        <v>1364</v>
+        <v>170</v>
       </c>
       <c r="H11" t="n">
-        <v>48.85</v>
+        <v>27.77</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1262000</v>
+        <v>18170</v>
       </c>
       <c r="K11" t="n">
-        <v>1290000</v>
+        <v>18340</v>
       </c>
       <c r="L11" t="n">
-        <v>1318000</v>
+        <v>18990</v>
       </c>
       <c r="M11" t="n">
-        <v>1247000</v>
+        <v>18110</v>
       </c>
       <c r="N11" t="n">
-        <v>49.02</v>
+        <v>27.82</v>
       </c>
       <c r="O11" t="n">
-        <v>3712819328500</v>
+        <v>39607406155</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q11" t="n">
-        <v>420500</v>
+        <v>17210</v>
       </c>
       <c r="R11" t="n">
-        <v>-448000</v>
+        <v>311000</v>
       </c>
       <c r="S11" t="n">
-        <v>-27000</v>
+        <v>156000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>최태원 회장에게 주가 관리 촉구. 연준 의장 연설 및 지정학적 이슈 언급. 외국인 매도 지속.</t>
+          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가 관리', '외국인', '솔리다임']</t>
+          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13430</v>
+        <v>42050</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.83%</t>
+          <t>'+3.19%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>259</v>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="G12" t="n">
-        <v>208</v>
+        <v>1009</v>
       </c>
       <c r="H12" t="n">
-        <v>3.42</v>
+        <v>12.97</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,130 +1515,130 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13060</v>
+        <v>40750</v>
       </c>
       <c r="K12" t="n">
-        <v>13390</v>
+        <v>40600</v>
       </c>
       <c r="L12" t="n">
-        <v>13620</v>
+        <v>42300</v>
       </c>
       <c r="M12" t="n">
-        <v>12910</v>
+        <v>40050</v>
       </c>
       <c r="N12" t="n">
-        <v>3.21</v>
+        <v>12.84</v>
       </c>
       <c r="O12" t="n">
-        <v>40542319235</v>
+        <v>13504493075</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>69200</v>
       </c>
       <c r="Q12" t="n">
-        <v>1640</v>
+        <v>24150</v>
       </c>
       <c r="R12" t="n">
-        <v>-62000</v>
+        <v>62000</v>
       </c>
       <c r="S12" t="n">
-        <v>-11000</v>
+        <v>-5000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
+          <t>CLASS1 발표 임박 및 FDA 승인 기대감. 담관암 치료제 관련 긍정적 전망 제기. 미선물 동향 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '미국장 반등']</t>
+          <t>['CLASS1', 'FDA 승인', '담관암']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>41900</v>
+        <v>1300000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.82%</t>
+          <t>'+3.01%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.13</v>
+        <v>-0.17</v>
       </c>
       <c r="E13" t="n">
-        <v>252</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>133</v>
+        <v>510</v>
       </c>
       <c r="G13" t="n">
-        <v>989</v>
+        <v>1332</v>
       </c>
       <c r="H13" t="n">
-        <v>12.97</v>
+        <v>48.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>40750</v>
+        <v>1262000</v>
       </c>
       <c r="K13" t="n">
-        <v>40600</v>
+        <v>1290000</v>
       </c>
       <c r="L13" t="n">
-        <v>42300</v>
+        <v>1318000</v>
       </c>
       <c r="M13" t="n">
-        <v>40050</v>
+        <v>1247000</v>
       </c>
       <c r="N13" t="n">
-        <v>12.84</v>
+        <v>49.02</v>
       </c>
       <c r="O13" t="n">
-        <v>13202584800</v>
+        <v>3809755381500</v>
       </c>
       <c r="P13" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>24150</v>
+        <v>420500</v>
       </c>
       <c r="R13" t="n">
-        <v>15000</v>
+        <v>-545000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-104000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>CLASS1 발표 임박 및 FDA 승인 기대감. 담관암 치료제 관련 긍정적 전망 제기. 미선물 동향 언급.</t>
+          <t>최태원 회장 주가 관리 부재 및 솔리다임 상장 이슈로 인한 주주 불만 고조. 연준 의장 연설, AI 시대 금융 제공 관련 언급. 외국인 매도세 지속.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['CLASS1', 'FDA 승인', '담관암']</t>
+          <t>['솔리다임', '외국인 매도', '주가 관리']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,86 +1660,86 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15040</v>
+        <v>13440</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.52%</t>
+          <t>'+2.91%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>181</v>
+        <v>56</v>
       </c>
       <c r="F14" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G14" t="n">
-        <v>398</v>
+        <v>215</v>
       </c>
       <c r="H14" t="n">
-        <v>9.779999999999999</v>
+        <v>3.42</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14670</v>
+        <v>13060</v>
       </c>
       <c r="K14" t="n">
-        <v>14800</v>
+        <v>13390</v>
       </c>
       <c r="L14" t="n">
-        <v>15270</v>
+        <v>13620</v>
       </c>
       <c r="M14" t="n">
-        <v>14800</v>
+        <v>12910</v>
       </c>
       <c r="N14" t="n">
-        <v>9.710000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="O14" t="n">
-        <v>29651311115</v>
+        <v>41494857255</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>1640</v>
       </c>
       <c r="R14" t="n">
-        <v>-92000</v>
+        <v>-119000</v>
       </c>
       <c r="S14" t="n">
-        <v>7000</v>
+        <v>-11000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>단일판매·공급계약 체결 공시 확인. 주가 조작 및 금감원 사모펀드 점검 관련 언급. 외인 보유율 유지 관련 언급.</t>
+          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공시', '주가 조작', '외국인']</t>
+          <t>['광통신', '야간선물', '미국장 반등']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,95 +1747,95 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15300</v>
+        <v>15030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.41%</t>
+          <t>'+2.45%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="F15" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>219</v>
+        <v>412</v>
       </c>
       <c r="H15" t="n">
-        <v>0.11</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14940</v>
+        <v>14670</v>
       </c>
       <c r="K15" t="n">
-        <v>14940</v>
+        <v>14800</v>
       </c>
       <c r="L15" t="n">
-        <v>16290</v>
+        <v>15270</v>
       </c>
       <c r="M15" t="n">
-        <v>14330</v>
+        <v>14800</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>45233812335</v>
+        <v>30232106775</v>
       </c>
       <c r="P15" t="n">
-        <v>30800</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>9810</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>7000</v>
+        <v>-130000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-47000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>상장 사기 및 높은 공모가 비판. 경영진 사퇴 요구 및 자진상폐 촉구.</t>
+          <t>1.43조원 규모 공급계약(상도15구역) 체결 공시 확인. 내년 건설주 상승 전망 및 대차 해지 중요성 강조. 주가 조작 관련 언급은 감정적 요소.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['상장 사기', '공모가', '경영진']</t>
+          <t>['공시', '공급계약', '건설주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23650</v>
+        <v>23600</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.94%</t>
+          <t>'+1.72%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="H16" t="n">
         <v>9.23</v>
@@ -1898,7 +1898,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>39266909900</v>
+        <v>40059518025</v>
       </c>
       <c r="P16" t="n">
         <v>24950</v>
@@ -1907,10 +1907,10 @@
         <v>17910</v>
       </c>
       <c r="R16" t="n">
-        <v>435000</v>
+        <v>565000</v>
       </c>
       <c r="S16" t="n">
-        <v>-20000</v>
+        <v>4000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20700</v>
+        <v>20750</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.24%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2.5</v>
       </c>
       <c r="E17" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F17" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17" t="n">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="H17" t="n">
         <v>4.28</v>
@@ -1990,7 +1990,7 @@
         <v>1.78</v>
       </c>
       <c r="O17" t="n">
-        <v>66960487370</v>
+        <v>67809446545</v>
       </c>
       <c r="P17" t="n">
         <v>22450</v>
@@ -1999,14 +1999,14 @@
         <v>6320</v>
       </c>
       <c r="R17" t="n">
-        <v>28000</v>
+        <v>-63000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>신규 납품 요청 및 보안 투자 확대 뉴스 기반. 양자보안 관련 기대감. 외인 및 연기금 매수세 확인.</t>
+          <t>농협, KDB 등 신규 납품 요청 및 보안 방패 관련 뉴스 언급. 양자보안 기대감 속에 주가 상승 전망. 공매도 및 연기금 동향 관련 분석.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['양자보안', '납품', '보안 투자']</t>
+          <t>['양자보안', '신규 납품', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,27 +2039,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26700</v>
+        <v>26900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-9.34%</t>
+          <t>'-8.66%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F18" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G18" t="n">
-        <v>473</v>
+        <v>521</v>
       </c>
       <c r="H18" t="n">
-        <v>53.38</v>
+        <v>53.36</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>138657475475</v>
+        <v>143285273325</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>
@@ -2091,14 +2091,14 @@
         <v>21000</v>
       </c>
       <c r="R18" t="n">
-        <v>-355000</v>
+        <v>-408000</v>
       </c>
       <c r="S18" t="n">
-        <v>-111000</v>
+        <v>-244000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 발표 후 배당 기대감 속 저점 매수 기회 언급. 외국인 매도 및 주가 하락 전망 제기.</t>
+          <t>실적 발표 후 저점 매수 기회 언급 있으나, 외국인 매도 시작 및 하락 VI 발동 가능성, 일봉 차트 훼손 등 부정적 전망이 우세.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['배당', '실적', '외국인']</t>
+          <t>['실적', '외국인 매도', '하락 VI']</t>
         </is>
       </c>
       <c r="X18" t="n">

--- a/data/trending_integrated_20261016_13.xlsx
+++ b/data/trending_integrated_20261016_13.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8040</v>
+        <v>8750</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.37%</t>
+          <t>'+22.38%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.26</v>
+        <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="F2" t="n">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="G2" t="n">
-        <v>218</v>
+        <v>306</v>
       </c>
       <c r="H2" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,38 +595,38 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6570</v>
+        <v>7150</v>
       </c>
       <c r="K2" t="n">
-        <v>6850</v>
+        <v>7430</v>
       </c>
       <c r="L2" t="n">
-        <v>8540</v>
+        <v>8970</v>
       </c>
       <c r="M2" t="n">
-        <v>6630</v>
+        <v>7300</v>
       </c>
       <c r="N2" t="n">
-        <v>0.99</v>
+        <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>73213665415</v>
+        <v>205124505795</v>
       </c>
       <c r="P2" t="n">
-        <v>10300</v>
+        <v>8970</v>
       </c>
       <c r="Q2" t="n">
-        <v>952</v>
+        <v>2270</v>
       </c>
       <c r="R2" t="n">
-        <v>-9000</v>
+        <v>36000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>군공항 이전 관련 언급 및 호남 반도체 관련주 상승 기대. 투경 및 급락 주의보, 외인 매수 전환 가능성 등 단기 변동성에 대한 다양한 의견.</t>
+          <t>인수합병 기대감 및 뉴로메가 편입 사례 비교로 인한 높은 기대감 존재. 단기 급등 후 차익 실현 움직임 관찰.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,11 +635,11 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['군공항 이전', '호남 반도체', '투경']</t>
+          <t>['인수합병', '로보틱스', '기대감']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8740</v>
+        <v>7980</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.24%</t>
+          <t>'+21.46%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.12</v>
+        <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="F3" t="n">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G3" t="n">
-        <v>299</v>
+        <v>225</v>
       </c>
       <c r="H3" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7150</v>
+        <v>6570</v>
       </c>
       <c r="K3" t="n">
-        <v>7430</v>
+        <v>6850</v>
       </c>
       <c r="L3" t="n">
-        <v>8970</v>
+        <v>8540</v>
       </c>
       <c r="M3" t="n">
-        <v>7300</v>
+        <v>6630</v>
       </c>
       <c r="N3" t="n">
-        <v>1.84</v>
+        <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>203400663915</v>
+        <v>74092834005</v>
       </c>
       <c r="P3" t="n">
-        <v>8970</v>
+        <v>10300</v>
       </c>
       <c r="Q3" t="n">
-        <v>2270</v>
+        <v>952</v>
       </c>
       <c r="R3" t="n">
-        <v>36000</v>
+        <v>-9000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>인수합병 가능성 및 텐버거 기대감 있으나, 검은머리 외국인 향방, 매도 대응 언급 등 단기적 등락에 대한 혼재된 의견.</t>
+          <t>군공항 이전 관련 언급 및 호남 반도체 관련주 상승 기대. 투경 및 급락 주의보, 외인 매수 전환 가능성 등 단기 변동성에 대한 다양한 의견.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['인수합병', '텐버거', '단타']</t>
+          <t>['군공항 이전', '호남 반도체', '투경']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8160</v>
+        <v>8200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.13%</t>
+          <t>'+14.69%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>50863624055</v>
+        <v>51067949225</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9610</v>
+        <v>9590</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.71%</t>
+          <t>'+8.48%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>86799518455</v>
+        <v>87354154130</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -931,92 +931,92 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10410</v>
+        <v>16080</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.83%</t>
+          <t>'+7.63%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>202</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="G6" t="n">
-        <v>145</v>
+        <v>228</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9930</v>
+        <v>14940</v>
       </c>
       <c r="K6" t="n">
-        <v>10100</v>
+        <v>14940</v>
       </c>
       <c r="L6" t="n">
-        <v>11100</v>
+        <v>16350</v>
       </c>
       <c r="M6" t="n">
-        <v>9860</v>
+        <v>14330</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>31891008865</v>
+        <v>58661386875</v>
       </c>
       <c r="P6" t="n">
-        <v>19380</v>
+        <v>30800</v>
       </c>
       <c r="Q6" t="n">
-        <v>3200</v>
+        <v>9810</v>
       </c>
       <c r="R6" t="n">
-        <v>-121000</v>
+        <v>6000</v>
       </c>
       <c r="S6" t="n">
-        <v>-8000</v>
+        <v>2000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
+          <t>상장 사기 및 높은 공모가 비판. 경영진 사퇴 요구 및 자진상폐 촉구.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
+          <t>['상장 사기', '공모가', '경영진']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="G7" t="n">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="H7" t="n">
         <v>45.98</v>
@@ -1070,7 +1070,7 @@
         <v>46.16</v>
       </c>
       <c r="O7" t="n">
-        <v>2510362927750</v>
+        <v>2557900574000</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>금감원, 이재명 관련 논란 속 대책 논의. 미국 CNBC 보도 및 애플의 중국산 반도체 사용 검토 뉴스. 개인 투자자들의 부정적 전망과 기대 혼재.</t>
+          <t>정치적 이슈와 반도체 업황에 대한 부정적 전망 속 단기적 주가 상승 기대감 혼재. 외인/기관 매도세 관찰.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['이재명', '금감원', 'CNBC']</t>
+          <t>['반도체', '전망', '외인']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,123 +1115,123 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18170</v>
+        <v>10350</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.01%</t>
+          <t>'+4.23%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>378</v>
+        <v>146</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>17470</v>
+        <v>9930</v>
       </c>
       <c r="K8" t="n">
-        <v>18710</v>
+        <v>10100</v>
       </c>
       <c r="L8" t="n">
-        <v>20300</v>
+        <v>11100</v>
       </c>
       <c r="M8" t="n">
-        <v>17630</v>
+        <v>9860</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>155789369280</v>
+        <v>32035757745</v>
       </c>
       <c r="P8" t="n">
-        <v>28800</v>
+        <v>19380</v>
       </c>
       <c r="Q8" t="n">
-        <v>15780</v>
+        <v>3200</v>
       </c>
       <c r="R8" t="n">
-        <v>4000</v>
+        <v>-121000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>반도체 테마 관련 언급 있으나, 장세 및 시가총액 고려 시 고평가 우려. 단일계좌 투주 이슈 및 단기 급락 가능성 경고.</t>
+          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체 테마', '단일계좌', '고평가']</t>
+          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15530</v>
+        <v>18170</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.95%</t>
+          <t>'+4.01%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="F9" t="n">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="G9" t="n">
-        <v>224</v>
+        <v>378</v>
       </c>
       <c r="H9" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14940</v>
+        <v>17470</v>
       </c>
       <c r="K9" t="n">
-        <v>14940</v>
+        <v>18710</v>
       </c>
       <c r="L9" t="n">
-        <v>16290</v>
+        <v>20300</v>
       </c>
       <c r="M9" t="n">
-        <v>14330</v>
+        <v>17630</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>50437359945</v>
+        <v>157308026465</v>
       </c>
       <c r="P9" t="n">
-        <v>30800</v>
+        <v>28800</v>
       </c>
       <c r="Q9" t="n">
-        <v>9810</v>
+        <v>15780</v>
       </c>
       <c r="R9" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="S9" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>상장 사기 및 높은 공모가 비판. 경영진 사퇴 요구 및 자진상폐 촉구.</t>
+          <t>고평가 및 시장 자금 부족으로 인한 상승 동력 약화 전망. 단기적 변동성 및 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['상장 사기', '공모가', '경영진']</t>
+          <t>['고평가', '테마', '변동성']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
         <v>88</v>
       </c>
       <c r="G10" t="n">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="H10" t="n">
         <v>22.1</v>
@@ -1346,7 +1346,7 @@
         <v>22.11</v>
       </c>
       <c r="O10" t="n">
-        <v>100640667500</v>
+        <v>101483521700</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>뉴스케일파워 상승 마감 및 원전 관련 언급. 3분기 매출 하회 예상 및 신용 매도 지적.</t>
+          <t>뉴스케일파워 상승 등 긍정적 소식에도 불구하고 주가 신뢰도 및 주주환원 정책에 대한 불만 제기. 실적 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['뉴스케일파워', '원전', '매출']</t>
+          <t>['원전', '주주환원', '실적']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18800</v>
+        <v>18840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.47%</t>
+          <t>'+3.69%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>34</v>
       </c>
       <c r="G11" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H11" t="n">
         <v>27.77</v>
@@ -1438,7 +1438,7 @@
         <v>27.82</v>
       </c>
       <c r="O11" t="n">
-        <v>39607406155</v>
+        <v>40182606940</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42050</v>
+        <v>42175</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.19%</t>
+          <t>'+3.50%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.13</v>
       </c>
       <c r="E12" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F12" t="n">
         <v>136</v>
       </c>
       <c r="G12" t="n">
-        <v>1009</v>
+        <v>1026</v>
       </c>
       <c r="H12" t="n">
         <v>12.97</v>
@@ -1530,7 +1530,7 @@
         <v>12.84</v>
       </c>
       <c r="O12" t="n">
-        <v>13504493075</v>
+        <v>13721519675</v>
       </c>
       <c r="P12" t="n">
         <v>69200</v>
@@ -1575,79 +1575,79 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1300000</v>
+        <v>13450</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.01%</t>
+          <t>'+2.99%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.17</v>
+        <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>510</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>1332</v>
+        <v>219</v>
       </c>
       <c r="H13" t="n">
-        <v>48.85</v>
+        <v>3.42</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1262000</v>
+        <v>13060</v>
       </c>
       <c r="K13" t="n">
-        <v>1290000</v>
+        <v>13390</v>
       </c>
       <c r="L13" t="n">
-        <v>1318000</v>
+        <v>13620</v>
       </c>
       <c r="M13" t="n">
-        <v>1247000</v>
+        <v>12910</v>
       </c>
       <c r="N13" t="n">
-        <v>49.02</v>
+        <v>3.21</v>
       </c>
       <c r="O13" t="n">
-        <v>3809755381500</v>
+        <v>42074129310</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q13" t="n">
-        <v>420500</v>
+        <v>1640</v>
       </c>
       <c r="R13" t="n">
-        <v>-545000</v>
+        <v>-119000</v>
       </c>
       <c r="S13" t="n">
-        <v>-104000</v>
+        <v>-11000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>최태원 회장 주가 관리 부재 및 솔리다임 상장 이슈로 인한 주주 불만 고조. 연준 의장 연설, AI 시대 금융 제공 관련 언급. 외국인 매도세 지속.</t>
+          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['솔리다임', '외국인 매도', '주가 관리']</t>
+          <t>['광통신', '야간선물', '미국장 반등']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,91 +1655,91 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13440</v>
+        <v>1299000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.91%</t>
+          <t>'+2.93%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="E14" t="n">
-        <v>56</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>35</v>
+        <v>501</v>
       </c>
       <c r="G14" t="n">
-        <v>215</v>
+        <v>1296</v>
       </c>
       <c r="H14" t="n">
-        <v>3.42</v>
+        <v>48.85</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13060</v>
+        <v>1262000</v>
       </c>
       <c r="K14" t="n">
-        <v>13390</v>
+        <v>1290000</v>
       </c>
       <c r="L14" t="n">
-        <v>13620</v>
+        <v>1318000</v>
       </c>
       <c r="M14" t="n">
-        <v>12910</v>
+        <v>1247000</v>
       </c>
       <c r="N14" t="n">
-        <v>3.21</v>
+        <v>49.02</v>
       </c>
       <c r="O14" t="n">
-        <v>41494857255</v>
+        <v>3873629881000</v>
       </c>
       <c r="P14" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>1640</v>
+        <v>420500</v>
       </c>
       <c r="R14" t="n">
-        <v>-119000</v>
+        <v>-545000</v>
       </c>
       <c r="S14" t="n">
-        <v>-11000</v>
+        <v>-104000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
+          <t>주가 관리 부재 및 정치적 요인에 따른 외국인 매도세 지적. 솔리다임 상장 이슈와 전고점 대비 큰 폭 하락 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '미국장 반등']</t>
+          <t>['주가관리', '외국인', '하락']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1774,13 +1774,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F15" t="n">
         <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="H15" t="n">
         <v>9.779999999999999</v>
@@ -1806,7 +1806,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>30232106775</v>
+        <v>30932105780</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.43조원 규모 공급계약(상도15구역) 체결 공시 확인. 내년 건설주 상승 전망 및 대차 해지 중요성 강조. 주가 조작 관련 언급은 감정적 요소.</t>
+          <t>1.43조원 규모 공급계약 체결 등 대형 공시 기반 긍정적 전망. 주가조작 및 사모펀드 관련 부정적 언급도 공존.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공시', '공급계약', '건설주']</t>
+          <t>['공급계약', '공시', '재개발']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23600</v>
+        <v>23550</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.72%</t>
+          <t>'+1.51%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="H16" t="n">
         <v>9.23</v>
@@ -1898,7 +1898,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>40059518025</v>
+        <v>40570068650</v>
       </c>
       <c r="P16" t="n">
         <v>24950</v>
@@ -1958,13 +1958,13 @@
         <v>2.5</v>
       </c>
       <c r="E17" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F17" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G17" t="n">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="H17" t="n">
         <v>4.28</v>
@@ -1990,7 +1990,7 @@
         <v>1.78</v>
       </c>
       <c r="O17" t="n">
-        <v>67809446545</v>
+        <v>68413800870</v>
       </c>
       <c r="P17" t="n">
         <v>22450</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>농협, KDB 등 신규 납품 요청 및 보안 방패 관련 뉴스 언급. 양자보안 기대감 속에 주가 상승 전망. 공매도 및 연기금 동향 관련 분석.</t>
+          <t>신규 납품 요청 및 보안 투자 확대 뉴스 기반 긍정적 전망. 해킹 사고 및 주가 급등 기대감 혼재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['양자보안', '신규 납품', '공매도']</t>
+          <t>['양자보안', '납품', '보안투자']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="F18" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G18" t="n">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="H18" t="n">
         <v>53.36</v>
@@ -2082,7 +2082,7 @@
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>143285273325</v>
+        <v>146541644125</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>

--- a/data/trending_integrated_20261016_13.xlsx
+++ b/data/trending_integrated_20261016_13.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8750</v>
+        <v>8120</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.38%</t>
+          <t>'+23.59%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.12</v>
+        <v>-0.26</v>
       </c>
       <c r="E2" t="n">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="F2" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="G2" t="n">
-        <v>306</v>
+        <v>234</v>
       </c>
       <c r="H2" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7150</v>
+        <v>6570</v>
       </c>
       <c r="K2" t="n">
-        <v>7430</v>
+        <v>6850</v>
       </c>
       <c r="L2" t="n">
-        <v>8970</v>
+        <v>8540</v>
       </c>
       <c r="M2" t="n">
-        <v>7300</v>
+        <v>6630</v>
       </c>
       <c r="N2" t="n">
-        <v>1.84</v>
+        <v>0.99</v>
       </c>
       <c r="O2" t="n">
-        <v>205124505795</v>
+        <v>76693856380</v>
       </c>
       <c r="P2" t="n">
-        <v>8970</v>
+        <v>10300</v>
       </c>
       <c r="Q2" t="n">
-        <v>2270</v>
+        <v>952</v>
       </c>
       <c r="R2" t="n">
-        <v>36000</v>
+        <v>-9000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>인수합병 기대감 및 뉴로메가 편입 사례 비교로 인한 높은 기대감 존재. 단기 급등 후 차익 실현 움직임 관찰.</t>
+          <t>매수세 유입 및 신고가 돌파 기대. 단기 급등 후 차익 실현 및 급락 주의.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['인수합병', '로보틱스', '기대감']</t>
+          <t>['신고가', '매집', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7980</v>
+        <v>8800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.46%</t>
+          <t>'+23.08%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.26</v>
+        <v>-1.12</v>
       </c>
       <c r="E3" t="n">
-        <v>107</v>
+        <v>172</v>
       </c>
       <c r="F3" t="n">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="G3" t="n">
-        <v>225</v>
+        <v>303</v>
       </c>
       <c r="H3" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6570</v>
+        <v>7150</v>
       </c>
       <c r="K3" t="n">
-        <v>6850</v>
+        <v>7430</v>
       </c>
       <c r="L3" t="n">
-        <v>8540</v>
+        <v>8970</v>
       </c>
       <c r="M3" t="n">
-        <v>6630</v>
+        <v>7300</v>
       </c>
       <c r="N3" t="n">
-        <v>0.99</v>
+        <v>1.84</v>
       </c>
       <c r="O3" t="n">
-        <v>74092834005</v>
+        <v>208449626515</v>
       </c>
       <c r="P3" t="n">
-        <v>10300</v>
+        <v>8970</v>
       </c>
       <c r="Q3" t="n">
-        <v>952</v>
+        <v>2270</v>
       </c>
       <c r="R3" t="n">
-        <v>-9000</v>
+        <v>36000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>군공항 이전 관련 언급 및 호남 반도체 관련주 상승 기대. 투경 및 급락 주의보, 외인 매수 전환 가능성 등 단기 변동성에 대한 다양한 의견.</t>
+          <t>인수합병 가능성 및 텐버거 기대감 있으나, 검은머리 외국인 향방, 매도 대응 언급 등 단기적 등락에 대한 혼재된 의견.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['군공항 이전', '호남 반도체', '투경']</t>
+          <t>['인수합병', '텐버거', '단타']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8200</v>
+        <v>8280</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.69%</t>
+          <t>'+15.80%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4" t="n">
         <v>253</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>51067949225</v>
+        <v>51524507875</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9590</v>
+        <v>9670</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.48%</t>
+          <t>'+9.39%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
         <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>87354154130</v>
+        <v>89221178585</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16080</v>
+        <v>15720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.63%</t>
+          <t>'+5.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="F6" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G6" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="H6" t="n">
         <v>0.11</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>58661386875</v>
+        <v>62440464055</v>
       </c>
       <c r="P6" t="n">
         <v>30800</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>219000</v>
+        <v>10400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.29%</t>
+          <t>'+4.73%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
-        <v>497</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>1231</v>
+        <v>146</v>
       </c>
       <c r="H7" t="n">
-        <v>45.98</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>210000</v>
+        <v>9930</v>
       </c>
       <c r="K7" t="n">
-        <v>215000</v>
+        <v>10100</v>
       </c>
       <c r="L7" t="n">
-        <v>220500</v>
+        <v>11100</v>
       </c>
       <c r="M7" t="n">
-        <v>210500</v>
+        <v>9860</v>
       </c>
       <c r="N7" t="n">
-        <v>46.16</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2557900574000</v>
+        <v>32166008245</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>19380</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>3200</v>
       </c>
       <c r="R7" t="n">
-        <v>-231000</v>
+        <v>-121000</v>
       </c>
       <c r="S7" t="n">
-        <v>-192000</v>
+        <v>-8000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈와 반도체 업황에 대한 부정적 전망 속 단기적 주가 상승 기대감 혼재. 외인/기관 매도세 관찰.</t>
+          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반도체', '전망', '외인']</t>
+          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10350</v>
+        <v>219500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.23%</t>
+          <t>'+4.52%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>34</v>
+        <v>498</v>
       </c>
       <c r="G8" t="n">
-        <v>146</v>
+        <v>1190</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>45.98</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,143 +1147,143 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9930</v>
+        <v>210000</v>
       </c>
       <c r="K8" t="n">
-        <v>10100</v>
+        <v>215000</v>
       </c>
       <c r="L8" t="n">
-        <v>11100</v>
+        <v>220500</v>
       </c>
       <c r="M8" t="n">
-        <v>9860</v>
+        <v>210500</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>46.16</v>
       </c>
       <c r="O8" t="n">
-        <v>32035757745</v>
+        <v>2634408190250</v>
       </c>
       <c r="P8" t="n">
-        <v>19380</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>3200</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>-121000</v>
+        <v>-231000</v>
       </c>
       <c r="S8" t="n">
-        <v>-8000</v>
+        <v>-192000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
+          <t>정부 정책 및 노조 이슈로 인한 주가 하락 우려. 단기 반등 및 25만/30만 목표가 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
+          <t>['이평선', '외인/기관', '반도체']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18170</v>
+        <v>65900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.01%</t>
+          <t>'+4.11%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="F9" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="G9" t="n">
-        <v>378</v>
+        <v>472</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>17470</v>
+        <v>63300</v>
       </c>
       <c r="K9" t="n">
-        <v>18710</v>
+        <v>63900</v>
       </c>
       <c r="L9" t="n">
-        <v>20300</v>
+        <v>66200</v>
       </c>
       <c r="M9" t="n">
-        <v>17630</v>
+        <v>63500</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>22.11</v>
       </c>
       <c r="O9" t="n">
-        <v>157308026465</v>
+        <v>103461463300</v>
       </c>
       <c r="P9" t="n">
-        <v>28800</v>
+        <v>139200</v>
       </c>
       <c r="Q9" t="n">
-        <v>15780</v>
+        <v>57000</v>
       </c>
       <c r="R9" t="n">
-        <v>4000</v>
+        <v>78000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>고평가 및 시장 자금 부족으로 인한 상승 동력 약화 전망. 단기적 변동성 및 급락 가능성 언급.</t>
+          <t>뉴스케일파워 등 원전주 상승세. 스페이스X 선정 및 주주환원 정책 요구.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['고평가', '테마', '변동성']</t>
+          <t>['원전주', '뉴스케일파워', '주주환원']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,77 +1292,77 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>65800</v>
+        <v>42200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.95%</t>
+          <t>'+3.56%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>0.13</v>
       </c>
       <c r="E10" t="n">
-        <v>145</v>
+        <v>271</v>
       </c>
       <c r="F10" t="n">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="G10" t="n">
-        <v>467</v>
+        <v>1068</v>
       </c>
       <c r="H10" t="n">
-        <v>22.1</v>
+        <v>12.97</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>63300</v>
+        <v>40750</v>
       </c>
       <c r="K10" t="n">
-        <v>63900</v>
+        <v>40600</v>
       </c>
       <c r="L10" t="n">
-        <v>66200</v>
+        <v>42300</v>
       </c>
       <c r="M10" t="n">
-        <v>63500</v>
+        <v>40050</v>
       </c>
       <c r="N10" t="n">
-        <v>22.11</v>
+        <v>12.84</v>
       </c>
       <c r="O10" t="n">
-        <v>101483521700</v>
+        <v>14080015250</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>78000</v>
+        <v>62000</v>
       </c>
       <c r="S10" t="n">
-        <v>11000</v>
+        <v>-5000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>뉴스케일파워 상승 등 긍정적 소식에도 불구하고 주가 신뢰도 및 주주환원 정책에 대한 불만 제기. 실적 관련 부정적 언급.</t>
+          <t>CLASS1 발표 임박 및 FDA 승인 기대감. 담관암 치료제 관련 긍정적 전망 제기. 미선물 동향 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '주주환원', '실적']</t>
+          <t>['CLASS1', 'FDA 승인', '담관암']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18840</v>
+        <v>18800</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.69%</t>
+          <t>'+3.47%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H11" t="n">
         <v>27.77</v>
@@ -1438,7 +1438,7 @@
         <v>27.82</v>
       </c>
       <c r="O11" t="n">
-        <v>40182606940</v>
+        <v>41395417410</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1483,70 +1483,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42175</v>
+        <v>1303000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.50%</t>
+          <t>'+3.25%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.13</v>
+        <v>-0.17</v>
       </c>
       <c r="E12" t="n">
-        <v>261</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>136</v>
+        <v>498</v>
       </c>
       <c r="G12" t="n">
-        <v>1026</v>
+        <v>1324</v>
       </c>
       <c r="H12" t="n">
-        <v>12.97</v>
+        <v>48.85</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>40750</v>
+        <v>1262000</v>
       </c>
       <c r="K12" t="n">
-        <v>40600</v>
+        <v>1290000</v>
       </c>
       <c r="L12" t="n">
-        <v>42300</v>
+        <v>1318000</v>
       </c>
       <c r="M12" t="n">
-        <v>40050</v>
+        <v>1247000</v>
       </c>
       <c r="N12" t="n">
-        <v>12.84</v>
+        <v>49.02</v>
       </c>
       <c r="O12" t="n">
-        <v>13721519675</v>
+        <v>3942079158000</v>
       </c>
       <c r="P12" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>24150</v>
+        <v>420500</v>
       </c>
       <c r="R12" t="n">
-        <v>62000</v>
+        <v>-545000</v>
       </c>
       <c r="S12" t="n">
-        <v>-5000</v>
+        <v>-104000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>CLASS1 발표 임박 및 FDA 승인 기대감. 담관암 치료제 관련 긍정적 전망 제기. 미선물 동향 언급.</t>
+          <t>최근 주가 급락에 대한 경영진 책임론. 정치적 이슈 및 솔리다임 상장 관련 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['CLASS1', 'FDA 승인', '담관암']</t>
+          <t>['주가 관리', '외국인', '솔리다임']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13450</v>
+        <v>18000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.99%</t>
+          <t>'+3.03%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="G13" t="n">
-        <v>219</v>
+        <v>381</v>
       </c>
       <c r="H13" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,139 +1607,139 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13060</v>
+        <v>17470</v>
       </c>
       <c r="K13" t="n">
-        <v>13390</v>
+        <v>18710</v>
       </c>
       <c r="L13" t="n">
-        <v>13620</v>
+        <v>20300</v>
       </c>
       <c r="M13" t="n">
-        <v>12910</v>
+        <v>17630</v>
       </c>
       <c r="N13" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>42074129310</v>
+        <v>158137750280</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>28800</v>
       </c>
       <c r="Q13" t="n">
-        <v>1640</v>
+        <v>15780</v>
       </c>
       <c r="R13" t="n">
-        <v>-119000</v>
+        <v>4000</v>
       </c>
       <c r="S13" t="n">
-        <v>-11000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
+          <t>고평가 논란 속 시가총액 저평가 주장. 주포의 움직임 및 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '미국장 반등']</t>
+          <t>['고평가', '시총', '주포']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1299000</v>
+        <v>13430</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.93%</t>
+          <t>'+2.83%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.17</v>
+        <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>58</v>
       </c>
       <c r="F14" t="n">
-        <v>501</v>
+        <v>35</v>
       </c>
       <c r="G14" t="n">
-        <v>1296</v>
+        <v>220</v>
       </c>
       <c r="H14" t="n">
-        <v>48.85</v>
+        <v>3.42</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1262000</v>
+        <v>13060</v>
       </c>
       <c r="K14" t="n">
-        <v>1290000</v>
+        <v>13390</v>
       </c>
       <c r="L14" t="n">
-        <v>1318000</v>
+        <v>13620</v>
       </c>
       <c r="M14" t="n">
-        <v>1247000</v>
+        <v>12910</v>
       </c>
       <c r="N14" t="n">
-        <v>49.02</v>
+        <v>3.21</v>
       </c>
       <c r="O14" t="n">
-        <v>3873629881000</v>
+        <v>42857464170</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q14" t="n">
-        <v>420500</v>
+        <v>1640</v>
       </c>
       <c r="R14" t="n">
-        <v>-545000</v>
+        <v>-119000</v>
       </c>
       <c r="S14" t="n">
-        <v>-104000</v>
+        <v>-11000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 관리 부재 및 정치적 요인에 따른 외국인 매도세 지적. 솔리다임 상장 이슈와 전고점 대비 큰 폭 하락 우려.</t>
+          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가관리', '외국인', '하락']</t>
+          <t>['광통신', '야간선물', '미국장 반등']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15030</v>
+        <v>15010</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.45%</t>
+          <t>'+2.32%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="F15" t="n">
         <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="H15" t="n">
         <v>9.779999999999999</v>
@@ -1806,7 +1806,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>30932105780</v>
+        <v>31485047945</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.43조원 규모 공급계약 체결 등 대형 공시 기반 긍정적 전망. 주가조작 및 사모펀드 관련 부정적 언급도 공존.</t>
+          <t>1.43조원 규모 공급 계약 체결. 건설주 상승 전망 및 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공급계약', '공시', '재개발']</t>
+          <t>['공시', '공급 계약', '건설주']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23550</v>
+        <v>23700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.51%</t>
+          <t>'+2.16%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="H16" t="n">
         <v>9.23</v>
@@ -1898,7 +1898,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>40570068650</v>
+        <v>41199580600</v>
       </c>
       <c r="P16" t="n">
         <v>24950</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20750</v>
+        <v>20700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.24%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2.5</v>
       </c>
       <c r="E17" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F17" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G17" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="H17" t="n">
         <v>4.28</v>
@@ -1990,7 +1990,7 @@
         <v>1.78</v>
       </c>
       <c r="O17" t="n">
-        <v>68413800870</v>
+        <v>68968701995</v>
       </c>
       <c r="P17" t="n">
         <v>22450</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>신규 납품 요청 및 보안 투자 확대 뉴스 기반 긍정적 전망. 해킹 사고 및 주가 급등 기대감 혼재.</t>
+          <t>양자보안 관련 긍정적 뉴스 및 신규 납품 요청. 보안 투자 확대 및 해킹 시도 증가.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['양자보안', '납품', '보안투자']</t>
+          <t>['양자보안', '납품', '보안 투자']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,27 +2039,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26900</v>
+        <v>26750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.66%</t>
+          <t>'-9.17%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="F18" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="G18" t="n">
-        <v>532</v>
+        <v>564</v>
       </c>
       <c r="H18" t="n">
-        <v>53.36</v>
+        <v>53.34</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>146541644125</v>
+        <v>151281978000</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 발표 후 저점 매수 기회 언급 있으나, 외국인 매도 시작 및 하락 VI 발동 가능성, 일봉 차트 훼손 등 부정적 전망이 우세.</t>
+          <t>실적 발표 후 외인/기관 대규모 매도에 따른 급락. 추가 하락 및 VI 발동 가능성 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적', '외국인 매도', '하락 VI']</t>
+          <t>['외인/기관', '실적 발표', '매도']</t>
         </is>
       </c>
       <c r="X18" t="n">

--- a/data/trending_integrated_20261016_13.xlsx
+++ b/data/trending_integrated_20261016_13.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8120</v>
+        <v>8860</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+23.59%</t>
+          <t>'+23.92%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.26</v>
+        <v>-1.12</v>
       </c>
       <c r="E2" t="n">
-        <v>114</v>
+        <v>181</v>
       </c>
       <c r="F2" t="n">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="G2" t="n">
-        <v>234</v>
+        <v>315</v>
       </c>
       <c r="H2" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6570</v>
+        <v>7150</v>
       </c>
       <c r="K2" t="n">
-        <v>6850</v>
+        <v>7430</v>
       </c>
       <c r="L2" t="n">
-        <v>8540</v>
+        <v>8970</v>
       </c>
       <c r="M2" t="n">
-        <v>6630</v>
+        <v>7300</v>
       </c>
       <c r="N2" t="n">
-        <v>0.99</v>
+        <v>1.84</v>
       </c>
       <c r="O2" t="n">
-        <v>76693856380</v>
+        <v>210830505715</v>
       </c>
       <c r="P2" t="n">
-        <v>10300</v>
+        <v>8970</v>
       </c>
       <c r="Q2" t="n">
-        <v>952</v>
+        <v>2270</v>
       </c>
       <c r="R2" t="n">
-        <v>-9000</v>
+        <v>36000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>매수세 유입 및 신고가 돌파 기대. 단기 급등 후 차익 실현 및 급락 주의.</t>
+          <t>합병 및 편입 관련 기대감 속 관망세. 단기 변동성과 개인 투자자들의 차익 실현 움직임.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신고가', '매집', '급등']</t>
+          <t>['인수합병', '편입', '거래량']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8800</v>
+        <v>8080</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+23.08%</t>
+          <t>'+22.98%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.12</v>
+        <v>-0.26</v>
       </c>
       <c r="E3" t="n">
-        <v>172</v>
+        <v>116</v>
       </c>
       <c r="F3" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="G3" t="n">
-        <v>303</v>
+        <v>239</v>
       </c>
       <c r="H3" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7150</v>
+        <v>6570</v>
       </c>
       <c r="K3" t="n">
-        <v>7430</v>
+        <v>6850</v>
       </c>
       <c r="L3" t="n">
-        <v>8970</v>
+        <v>8540</v>
       </c>
       <c r="M3" t="n">
-        <v>7300</v>
+        <v>6630</v>
       </c>
       <c r="N3" t="n">
-        <v>1.84</v>
+        <v>0.99</v>
       </c>
       <c r="O3" t="n">
-        <v>208449626515</v>
+        <v>77911422620</v>
       </c>
       <c r="P3" t="n">
-        <v>8970</v>
+        <v>10300</v>
       </c>
       <c r="Q3" t="n">
-        <v>2270</v>
+        <v>952</v>
       </c>
       <c r="R3" t="n">
-        <v>36000</v>
+        <v>-9000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>인수합병 가능성 및 텐버거 기대감 있으나, 검은머리 외국인 향방, 매도 대응 언급 등 단기적 등락에 대한 혼재된 의견.</t>
+          <t>매수세 유입 및 신고가 돌파 기대. 단기 급등 후 차익 실현 및 급락 주의.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['인수합병', '텐버거', '단타']</t>
+          <t>['신고가', '매집', '급등']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8280</v>
+        <v>8270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.80%</t>
+          <t>'+15.66%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>51524507875</v>
+        <v>51918315055</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9670</v>
+        <v>9620</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.39%</t>
+          <t>'+8.82%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>89221178585</v>
+        <v>89890851045</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15720</v>
+        <v>16060</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.22%</t>
+          <t>'+7.50%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="F6" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G6" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="H6" t="n">
         <v>0.11</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>62440464055</v>
+        <v>65936600350</v>
       </c>
       <c r="P6" t="n">
         <v>30800</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10400</v>
+        <v>220000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.73%</t>
+          <t>'+4.76%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>501</v>
       </c>
       <c r="G7" t="n">
-        <v>146</v>
+        <v>1178</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>45.98</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9930</v>
+        <v>210000</v>
       </c>
       <c r="K7" t="n">
-        <v>10100</v>
+        <v>215000</v>
       </c>
       <c r="L7" t="n">
-        <v>11100</v>
+        <v>220500</v>
       </c>
       <c r="M7" t="n">
-        <v>9860</v>
+        <v>210500</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>46.16</v>
       </c>
       <c r="O7" t="n">
-        <v>32166008245</v>
+        <v>2705859420000</v>
       </c>
       <c r="P7" t="n">
-        <v>19380</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>3200</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>-121000</v>
+        <v>-231000</v>
       </c>
       <c r="S7" t="n">
-        <v>-8000</v>
+        <v>-192000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
+          <t>정치적 이슈와 외인 매도세 언급 속, 단기 반등 기대감 존재. 반도체 업황에 대한 우려와 긍정적 전망 혼재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
+          <t>['이평선', '반도체', '외인']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>219500</v>
+        <v>10380</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.52%</t>
+          <t>'+4.53%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
-        <v>498</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>1190</v>
+        <v>148</v>
       </c>
       <c r="H8" t="n">
-        <v>45.98</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>210000</v>
+        <v>9930</v>
       </c>
       <c r="K8" t="n">
-        <v>215000</v>
+        <v>10100</v>
       </c>
       <c r="L8" t="n">
-        <v>220500</v>
+        <v>11100</v>
       </c>
       <c r="M8" t="n">
-        <v>210500</v>
+        <v>9860</v>
       </c>
       <c r="N8" t="n">
-        <v>46.16</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2634408190250</v>
+        <v>32318435995</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>19380</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>3200</v>
       </c>
       <c r="R8" t="n">
-        <v>-231000</v>
+        <v>-121000</v>
       </c>
       <c r="S8" t="n">
-        <v>-192000</v>
+        <v>-8000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정부 정책 및 노조 이슈로 인한 주가 하락 우려. 단기 반등 및 25만/30만 목표가 언급.</t>
+          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['이평선', '외인/기관', '반도체']</t>
+          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65900</v>
+        <v>66100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.11%</t>
+          <t>'+4.42%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F9" t="n">
         <v>88</v>
       </c>
       <c r="G9" t="n">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="H9" t="n">
         <v>22.1</v>
@@ -1254,7 +1254,7 @@
         <v>22.11</v>
       </c>
       <c r="O9" t="n">
-        <v>103461463300</v>
+        <v>105383371600</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42200</v>
+        <v>1309000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.56%</t>
+          <t>'+3.72%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.13</v>
+        <v>-0.17</v>
       </c>
       <c r="E10" t="n">
-        <v>271</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>136</v>
+        <v>496</v>
       </c>
       <c r="G10" t="n">
-        <v>1068</v>
+        <v>1296</v>
       </c>
       <c r="H10" t="n">
-        <v>12.97</v>
+        <v>48.85</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>40750</v>
+        <v>1262000</v>
       </c>
       <c r="K10" t="n">
-        <v>40600</v>
+        <v>1290000</v>
       </c>
       <c r="L10" t="n">
-        <v>42300</v>
+        <v>1318000</v>
       </c>
       <c r="M10" t="n">
-        <v>40050</v>
+        <v>1247000</v>
       </c>
       <c r="N10" t="n">
-        <v>12.84</v>
+        <v>49.02</v>
       </c>
       <c r="O10" t="n">
-        <v>14080015250</v>
+        <v>4028568966000</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>420500</v>
       </c>
       <c r="R10" t="n">
-        <v>62000</v>
+        <v>-545000</v>
       </c>
       <c r="S10" t="n">
-        <v>-5000</v>
+        <v>-104000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>CLASS1 발표 임박 및 FDA 승인 기대감. 담관암 치료제 관련 긍정적 전망 제기. 미선물 동향 언급.</t>
+          <t>정치적 요인과 외인 매도에 대한 강한 불만 표출. 주가 하락에 대한 비판과 함께 일부 기대감 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['CLASS1', 'FDA 승인', '담관암']</t>
+          <t>['주가관리', '외국인', '폭락']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,130 +1384,130 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18800</v>
+        <v>42200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.47%</t>
+          <t>'+3.56%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.05</v>
+        <v>0.13</v>
       </c>
       <c r="E11" t="n">
-        <v>56</v>
+        <v>273</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="G11" t="n">
-        <v>173</v>
+        <v>1110</v>
       </c>
       <c r="H11" t="n">
-        <v>27.77</v>
+        <v>12.97</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18170</v>
+        <v>40750</v>
       </c>
       <c r="K11" t="n">
-        <v>18340</v>
+        <v>40600</v>
       </c>
       <c r="L11" t="n">
-        <v>18990</v>
+        <v>42300</v>
       </c>
       <c r="M11" t="n">
-        <v>18110</v>
+        <v>40050</v>
       </c>
       <c r="N11" t="n">
-        <v>27.82</v>
+        <v>12.84</v>
       </c>
       <c r="O11" t="n">
-        <v>41395417410</v>
+        <v>14399136275</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>69200</v>
       </c>
       <c r="Q11" t="n">
-        <v>17210</v>
+        <v>24150</v>
       </c>
       <c r="R11" t="n">
-        <v>311000</v>
+        <v>62000</v>
       </c>
       <c r="S11" t="n">
-        <v>156000</v>
+        <v>-5000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
+          <t>FDA 승인 관련 기대감 속, 클래스 1 발표 가능성 및 임상 결과에 대한 논의. 과거 사례 언급하며 신중론도 제기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
+          <t>['FDA', '임상', '승인']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1303000</v>
+        <v>18810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.25%</t>
+          <t>'+3.52%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.17</v>
+        <v>-0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>56</v>
       </c>
       <c r="F12" t="n">
-        <v>498</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>1324</v>
+        <v>175</v>
       </c>
       <c r="H12" t="n">
-        <v>48.85</v>
+        <v>27.77</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,60 +1515,60 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1262000</v>
+        <v>18170</v>
       </c>
       <c r="K12" t="n">
-        <v>1290000</v>
+        <v>18340</v>
       </c>
       <c r="L12" t="n">
-        <v>1318000</v>
+        <v>18990</v>
       </c>
       <c r="M12" t="n">
-        <v>1247000</v>
+        <v>18110</v>
       </c>
       <c r="N12" t="n">
-        <v>49.02</v>
+        <v>27.82</v>
       </c>
       <c r="O12" t="n">
-        <v>3942079158000</v>
+        <v>42592434695</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>420500</v>
+        <v>17210</v>
       </c>
       <c r="R12" t="n">
-        <v>-545000</v>
+        <v>311000</v>
       </c>
       <c r="S12" t="n">
-        <v>-104000</v>
+        <v>156000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>최근 주가 급락에 대한 경영진 책임론. 정치적 이슈 및 솔리다임 상장 관련 우려.</t>
+          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주가 관리', '외국인', '솔리다임']</t>
+          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18000</v>
+        <v>18070</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.03%</t>
+          <t>'+3.43%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F13" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G13" t="n">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>158137750280</v>
+        <v>158778063745</v>
       </c>
       <c r="P13" t="n">
         <v>28800</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>고평가 논란 속 시가총액 저평가 주장. 주포의 움직임 및 급락 가능성 언급.</t>
+          <t>주가 상승 및 하락에 대한 상반된 전망. 반도체 테마 내에서의 저평가 논의 및 수급 불안정성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['고평가', '시총', '주포']</t>
+          <t>['저평가', '수급', '반도체']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13430</v>
+        <v>13470</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.83%</t>
+          <t>'+3.14%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="H14" t="n">
         <v>3.42</v>
@@ -1714,7 +1714,7 @@
         <v>3.21</v>
       </c>
       <c r="O14" t="n">
-        <v>42857464170</v>
+        <v>43750839350</v>
       </c>
       <c r="P14" t="n">
         <v>31500</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15010</v>
+        <v>15070</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.32%</t>
+          <t>'+2.73%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G15" t="n">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="H15" t="n">
         <v>9.779999999999999</v>
@@ -1806,7 +1806,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>31485047945</v>
+        <v>31975154435</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.43조원 규모 공급 계약 체결. 건설주 상승 전망 및 주가 조작 의혹 제기.</t>
+          <t>대규모 공급 계약 체결에 따른 실적 개선 기대감. 주가 조작 및 금감원 사모펀드 긴급 점검 관련 내용 포함.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공시', '공급 계약', '건설주']</t>
+          <t>['공급계약', '실적', '공시']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1866,13 +1866,13 @@
         <v>0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G16" t="n">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="H16" t="n">
         <v>9.23</v>
@@ -1898,7 +1898,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>41199580600</v>
+        <v>41764122550</v>
       </c>
       <c r="P16" t="n">
         <v>24950</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20700</v>
+        <v>20650</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.24%</t>
+          <t>'-0.48%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2.5</v>
       </c>
       <c r="E17" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G17" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H17" t="n">
         <v>4.28</v>
@@ -1990,7 +1990,7 @@
         <v>1.78</v>
       </c>
       <c r="O17" t="n">
-        <v>68968701995</v>
+        <v>69692668395</v>
       </c>
       <c r="P17" t="n">
         <v>22450</v>
@@ -2039,27 +2039,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26750</v>
+        <v>26700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-9.17%</t>
+          <t>'-9.34%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.19</v>
       </c>
       <c r="E18" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="F18" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G18" t="n">
-        <v>564</v>
+        <v>596</v>
       </c>
       <c r="H18" t="n">
-        <v>53.34</v>
+        <v>53.32</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>26.75</v>
       </c>
       <c r="O18" t="n">
-        <v>151281978000</v>
+        <v>155590625900</v>
       </c>
       <c r="P18" t="n">
         <v>32500</v>
